--- a/daily_matches/job_matches_2026-09-25.xlsx
+++ b/daily_matches/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, S3, Kinesis, FastAPI, CI/CD, Jenkins</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea65c9a95c2f071</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ed0115e6583c60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d939162f62431c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=beb4540fc449cc54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Pinecone, Prompt Engineering, S3, CI/CD, Git, PostgreSQL, MySQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
+          <t>https://www.indeed.com/viewjob?jk=07f29bd7335fb716</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quantitative Analyst, Artificial Intelligence/Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras</t>
+          <t>RAG, Prompt Engineering, PyTorch, MLflow, Kubernetes, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b660050ff9dd9f85</t>
+          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>Cortex, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hirschi Companies, LLC</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Azure ML, Synapse, CI/CD, Git, Databricks, PySpark, Power BI, Python</t>
+          <t>Generative AI, RAG, Cortex, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior SDET I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, S3, AKS, Apache Airflow, CI/CD, Git, Snowflake, Power BI</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41698f714a5488d9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd9f6a88f947060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hims &amp; hers</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, LightGBM, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75248895bf36eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (AI, Python, LLM, RAG, CI CD)</t>
+          <t>IT Developer Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chippewa Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3214b3b4a0bda089</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc9fb81e98d2ad5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (AI, Python, LLM, RAG, CI CD)</t>
+          <t>AI - Forward Deployed Engineer (contract)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493e960306c85416</t>
+          <t>https://www.indeed.com/viewjob?jk=a58836203020ab40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI Software Engineer | LLMs, RAG &amp; Private AI - Interview Today - Start Tomorrow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Beverly Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=600d896233b3b03b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>ZT Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
+          <t>https://www.indeed.com/viewjob?jk=eb7f73e583679602</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c22a9cd90d906b8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Partner Solutions Architect – GSI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Cortex, GCP Vertex AI, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
+          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
+          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8358d3c468076b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Athena, Kubernetes, Terraform, Hadoop, Python, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e33951936fab21</t>
+          <t>https://www.indeed.com/viewjob?jk=dbce4e95c145a21a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e5849960c5981</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer III, Media Solutions</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478ac73ea415376a</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd29896ffc37932</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Senior Software Engineer, Full-Stack Applications - Ratings Technology (New York)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stratus Data Systems</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315fefbf23d8f968</t>
+          <t>https://www.indeed.com/viewjob?jk=5d83f38d5ba2707d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Data Engineer, Data Platform</t>
+          <t>Senior Software Engineer, Full-Stack Applications - Ratings Technology (Chicago)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
+          <t>https://www.indeed.com/viewjob?jk=07ece509fb9624da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 3, Full-stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f411846eaae427d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1c268328c60618</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Distributed Systems Backend Engineer, Used Cars</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Git, Kafka, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,54 +1266,54 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86dd5dffc7a02b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a91e80ec69283</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps / Site Reliability Engineer</t>
+          <t>Associate Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed588442d76c75ae</t>
+          <t>https://www.indeed.com/viewjob?jk=952469627dbb56f2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps / Site Reliability Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Premera Blue Cross</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Matplotlib, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9537940d51f0f461</t>
+          <t>https://www.indeed.com/viewjob?jk=c18b155950d96539</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps / Site Reliability Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5be131e8ab2fea</t>
+          <t>https://www.indeed.com/viewjob?jk=aad34223177350c1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps / Site Reliability Engineer</t>
+          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0d15bbcf4d6a948</t>
+          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Engineer II, Full Stack (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6f7adb93ae18d</t>
+          <t>https://www.indeed.com/viewjob?jk=2976583b2e619dfe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0653a86397fec5d</t>
+          <t>https://www.indeed.com/viewjob?jk=898e0a0fbf7048b2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Microsoft Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>RAG, GitHub Actions, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e1876a23eec4014</t>
+          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Implementation Engineer (Remote)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Tealium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb6f7927a01365a</t>
+          <t>https://www.indeed.com/viewjob?jk=22a38c809b508ba1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Workflow Engineer</t>
+          <t>Sr Business Analyst, Applied Intelligence</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7248042eb3c60ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>alliantgroup</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168a1d8b39f7c377</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ee3634e195e67e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c4415fd9973a81</t>
+          <t>https://www.indeed.com/viewjob?jk=035d020318053c58</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Network Engineer- WAN (Sr. Consultant level)</t>
+          <t>Full Stack Engineer (Java &amp; React)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Terraform, Git, Python, R</t>
+          <t>RAG, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154636161da29c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=2312719462539b7d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CXO AI Engineer</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Redshift, Redshift, Python, SQL, R, Scala</t>
+          <t>RAG, Jenkins, Git, Hadoop, MicroStrategy, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb4d1a9d2cf1a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CXO AI Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Redshift, Redshift, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5a8075efccc2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7abf49b8281f0a4b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,367 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Docker, Kubernetes, Kafka, Cassandra, R, Scala</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Global Forwarding Technology</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, Kafka, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e57d6a26215db07c</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>DreamWorks Technology - Senior AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NBCUniversal</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f89e3d92865052</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Praxis Precision Medicines, Inc.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LENS</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Docker, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da892a01aa29c6ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=078a75ceea9a8452</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc84a35f669070ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=026213a9257bf62f</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=897ec09b6d9bf51d</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74ee1da0bb04a159</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>DocuSign</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69f63e93b40db154</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7ddda5e03cb3bc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-25.xlsx
+++ b/daily_matches/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,122 +468,122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>AI Engineer – Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Converge Squad 2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Randolph, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ed0115e6583c60</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fa8b7fddbde35f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb4540fc449cc54</t>
+          <t>https://www.indeed.com/viewjob?jk=f21fdd22f5784839</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Docker</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f29bd7335fb716</t>
+          <t>https://www.indeed.com/viewjob?jk=86944a11bfaac4a8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, PyTorch, MLflow, Kubernetes, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
+          <t>Generative AI, RAG, S3, EC2, Apache Airflow, CI/CD, Terraform, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cortex, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Power BI</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, PySpark, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
+          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior SDET I</t>
+          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>BigQuery, Dataflow, Docker, Kubernetes, CI/CD, BigQuery, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd9f6a88f947060</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Software Engineer-Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Tableau</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, Kafka, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
+          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Developer Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chippewa Falls, WI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc9fb81e98d2ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI - Forward Deployed Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, PyTorch, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58836203020ab40</t>
+          <t>https://www.indeed.com/viewjob?jk=b6396c083d147577</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Software Engineer | LLMs, RAG &amp; Private AI - Interview Today - Start Tomorrow</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, PyTorch, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600d896233b3b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9208a1a6a7f8bb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Agentic Operations Engineer 6491979</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZT Systems</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, Git</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb7f73e583679602</t>
+          <t>https://www.indeed.com/viewjob?jk=0a23b6eb87e91b6a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Kinesis, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c22a9cd90d906b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Partner Solutions Architect – GSI</t>
+          <t>Senior AI Engineer - Search, Personalization, Agents (Remote)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, GCP Vertex AI, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, Prompt Engineering, Glue, Docker, CI/CD, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc2a574dcde1540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
+          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8358d3c468076b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbce4e95c145a21a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Kubernetes, CI/CD, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6e5849960c5981</t>
+          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer III, Media Solutions</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd29896ffc37932</t>
+          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack Applications - Ratings Technology (New York)</t>
+          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d83f38d5ba2707d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack Applications - Ratings Technology (Chicago)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07ece509fb9624da</t>
+          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1c268328c60618</t>
+          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a91e80ec69283</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Full Stack Developer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=952469627dbb56f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Premera Blue Cross</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Matplotlib, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18b155950d96539</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad34223177350c1</t>
+          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II, Full Stack (Remote)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2976583b2e619dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898e0a0fbf7048b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Platform Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, GitHub Actions, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
+          <t>https://www.indeed.com/viewjob?jk=843ce198c1c04576</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Implementation Engineer (Remote)</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tealium</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a38c809b508ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04ef4604e476c6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Business Analyst, Applied Intelligence</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,217 +1581,1302 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
+          <t>https://www.indeed.com/viewjob?jk=fecc6c5f25f41ffc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ee3634e195e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=d48d24e36571ac6e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035d020318053c58</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2a2c8569c5046b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Java &amp; React)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2312719462539b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e410790f9b462e9f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, Hadoop, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
+          <t>https://www.indeed.com/viewjob?jk=52108bbcbb003e69</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7abf49b8281f0a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0cdc8d34a934bbc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=138e060c9ff0d615</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Engineer (175879)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Database Engineering) - Spring 2027</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, PyTorch, Snowflake, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797cb1062d93c38b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1daeddb12e219e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 5 (Java, Python, SRE, AWS, AI) (Cloud Operations Resilience Engineering)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f7d53abc5ab6e76</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Java, Python, AWS) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adb9b8a0e25ee1a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Engineer 5 (Python, SQL, Databricks, Snowflake) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9be429df1e6db22c</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=933acebcc1d91f93</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c40455ab9ed41ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior QA Engineer (L4)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mirantis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80556d2d1b3dfabf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GenAI Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15181df7de132b1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Backend Engineer – Python / FastAPI / Azure</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e094e8d70b960ebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AWS Application Support Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>vertage</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>S3, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27ae1f61d818d5de</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer (REMOTE)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Roadpass Digital</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, S3, Git, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f862aa1a4a7d3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI Harness Engineers</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=465f862bea37a035</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Azure DevOps &amp; Mobile Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f2aa1f84c9be552</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Azure DevOps &amp; Mobile Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Capgemini Engineering</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33c48b432f8a7501</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Harness Engineers</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bf88c29176749dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, Terraform, Snowflake, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cloud Engineer 4 (Cloud Operations Resilience Engineering)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59e3ab4f3220449d</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer, Network Intelligence</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, FastAPI, Docker, Kubernetes, AKS, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2150ddfa17f83ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>California Employment Development Department (EDD)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8de0430167cc6d52</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Scientist - QuantumBlack, AI by McKinsey</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>10</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7ddda5e03cb3bc</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f84ed2ba8dbfdc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Software Engineer - QuantumBlack, AI by McKinsey</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74f109f574e0030c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Engineer (Entry level)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>vertage</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Copilot, Glue, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69c84d37dd0553bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (West Coast USA)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fictiv</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, EC2, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f85a5971250cdb3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c253ea03e35bc155</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer (175810)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44a1b86cc703f06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DevOps Engineer Senior - Tempus</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da5c0f0177450ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist Online &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f94e65599902b68</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-25.xlsx
+++ b/daily_matches/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer – Senior Software Engineer</t>
+          <t>Senior Engineer, Big Data - Medical Cost Grouper - Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Converge Squad 2</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Randolph, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow</t>
+          <t>RAG, Copilot, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fa8b7fddbde35f</t>
+          <t>https://www.indeed.com/viewjob?jk=10ee7d4f1fc05ba7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, LangChain, Hugging Face, MLflow, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21fdd22f5784839</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Apache Airflow, Git, Snowflake, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86944a11bfaac4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=32617ffc4957d5bf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Apache Airflow, CI/CD, Terraform, Git, Databricks, PySpark</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, PySpark, MongoDB, Cassandra, NoSQL</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
+          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
+          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Docker, Kubernetes, CI/CD, BigQuery, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer-Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, Kafka, NoSQL, Python</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, PyTorch, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6396c083d147577</t>
+          <t>https://www.indeed.com/viewjob?jk=0aad97e5a348e806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, PyTorch, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9208a1a6a7f8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a781cd243af3ce9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Agentic Operations Engineer 6491979</t>
+          <t>Senior ML Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Data Scientist, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a23b6eb87e91b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=273b197ffada9aa9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Kinesis, Redshift, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Jenkins, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Search, Personalization, Agents (Remote)</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, Prompt Engineering, Glue, Docker, CI/CD, PySpark, Python, SQL</t>
+          <t>LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc2a574dcde1540</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,73 +972,73 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
+          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Jenkins, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Intern, Applications Engineering (2027)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hollister Incorporated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Libertyville, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2ed38779fa18a3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1086,772 +1086,772 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
+          <t>https://www.indeed.com/viewjob?jk=adb59a064cdc32b3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Full Time • On-Site</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cashfree Payments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lead, SD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, S3, EC2, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
+          <t>https://www.indeed.com/viewjob?jk=42c0a4e8e7657855</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
+          <t>Sr AI/ML Engineer Remote Nationwide or Office-Based in MN/DC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
+          <t>https://www.indeed.com/viewjob?jk=979d4ab5c26ffde8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Intern, IT Data Analytics (2027)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hollister Incorporated</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Synapse, Git, Databricks, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git, Databricks, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b74504de244a81e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Software Engineer, Backend (Python/C++)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a701ef357c36b69</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
+          <t>https://www.indeed.com/viewjob?jk=d775992305d45996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Glue, Athena, FastAPI, Apache Airflow, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
+          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
+          <t>Ai/Ml engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Mamsys World</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
+          <t>https://www.indeed.com/viewjob?jk=56c44f654a30eb41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Software Engineer 1 - Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
+          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
+          <t>Data Scientist - Financial Crimes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Matplotlib, Python, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
+          <t>https://www.indeed.com/viewjob?jk=acdcf48b7568b4d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843ce198c1c04576</t>
+          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04ef4604e476c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecc6c5f25f41ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48d24e36571ac6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2a2c8569c5046b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e410790f9b462e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52108bbcbb003e69</t>
+          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cdc8d34a934bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138e060c9ff0d615</t>
+          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer (175879)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Database Engineering) - Spring 2027</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, PyTorch, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,277 +1896,277 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797cb1062d93c38b</t>
+          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1daeddb12e219e0</t>
+          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5 (Java, Python, SRE, AWS, AI) (Cloud Operations Resilience Engineering)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7d53abc5ab6e76</t>
+          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS) (Enterprise Platforms Technology)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb9b8a0e25ee1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer 5 (Python, SQL, Databricks, Snowflake) (Enterprise Platforms Technology)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be429df1e6db22c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
+          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer - Artificial Intelligence</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933acebcc1d91f93</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer - Artificial Intelligence</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c40455ab9ed41ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior QA Engineer (L4)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80556d2d1b3dfabf</t>
+          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Python, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15181df7de132b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Backend Engineer – Python / FastAPI / Azure</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094e8d70b960ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Application Support Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S3, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ae1f61d818d5de</t>
+          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer (REMOTE)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Roadpass Digital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Git, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f862aa1a4a7d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Harness Engineers</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465f862bea37a035</t>
+          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure DevOps &amp; Mobile Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2aa1f84c9be552</t>
+          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure DevOps &amp; Mobile Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini Engineering</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c48b432f8a7501</t>
+          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Harness Engineers</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf88c29176749dc</t>
+          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Snowflake, Hadoop, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Engineer 4 (Cloud Operations Resilience Engineering)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59e3ab4f3220449d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer, Network Intelligence</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, FastAPI, Docker, Kubernetes, AKS, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2150ddfa17f83ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>California Employment Development Department (EDD)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de0430167cc6d52</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist - QuantumBlack, AI by McKinsey</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Python, SQL, R, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f84ed2ba8dbfdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f109f574e0030c</t>
+          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (Entry level)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Copilot, Glue, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c84d37dd0553bd</t>
+          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (West Coast USA)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fictiv</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RAG, Copilot, EC2, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85a5971250cdb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c253ea03e35bc155</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (175810)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a1b86cc703f06e</t>
+          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps Engineer Senior - Tempus</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5c0f0177450ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Scientist Online &amp; Marketing</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,532 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f94e65599902b68</t>
+          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior STIBO Software Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Concord, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Wausau, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Apache Airflow, CI/CD, Jenkins, Git, Snowflake, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Intern, Applied AI (2027)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hollister Incorporated</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Libertyville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9eb32bab99987ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sovos</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7451e1e1ecb30cae</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Engineering Internship</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chess.com</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, BigQuery, BigQuery, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2d507aff010c9ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Paramount</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4f00f7ccb96862</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Solutions Engineer (Pre-Sales)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1496abfaa43f97c3</t>
         </is>
       </c>
     </row>
